--- a/backend/DATA_UPCOMING.xlsx
+++ b/backend/DATA_UPCOMING.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\venv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9624A860-C5FF-408E-ADB9-C592A3FEA7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D7FD85-8D9F-4E42-91E1-599FFA62CF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2994,6 +2994,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF5B3F86"/>
@@ -3012,6 +3036,2342 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
           <bgColor rgb="FFF8F9FA"/>
         </patternFill>
@@ -3030,2342 +5390,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5388,6 +5412,86 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
           <bgColor rgb="FFF8F9FA"/>
         </patternFill>
@@ -5406,86 +5510,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5508,6 +5532,662 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
           <bgColor rgb="FFF8F9FA"/>
         </patternFill>
@@ -5526,662 +6206,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6220,408 +6244,408 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6641,37 +6665,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="330">
     <tableStyle name="SURVEY RESULTS-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="666"/>
-      <tableStyleElement type="headerRow" dxfId="669"/>
-      <tableStyleElement type="firstRowStripe" dxfId="668"/>
-      <tableStyleElement type="secondRowStripe" dxfId="667"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="669"/>
+      <tableStyleElement type="headerRow" dxfId="668"/>
+      <tableStyleElement type="firstRowStripe" dxfId="667"/>
+      <tableStyleElement type="secondRowStripe" dxfId="666"/>
     </tableStyle>
     <tableStyle name="2022 -2025 PRC DATA RECORD-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="665"/>
@@ -6774,10 +6774,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="616"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF1A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="612"/>
-      <tableStyleElement type="headerRow" dxfId="615"/>
-      <tableStyleElement type="firstRowStripe" dxfId="614"/>
-      <tableStyleElement type="secondRowStripe" dxfId="613"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="615"/>
+      <tableStyleElement type="headerRow" dxfId="614"/>
+      <tableStyleElement type="firstRowStripe" dxfId="613"/>
+      <tableStyleElement type="secondRowStripe" dxfId="612"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF1B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="611"/>
@@ -6944,10 +6944,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="530"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF44000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="526"/>
-      <tableStyleElement type="headerRow" dxfId="529"/>
-      <tableStyleElement type="firstRowStripe" dxfId="528"/>
-      <tableStyleElement type="secondRowStripe" dxfId="527"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="529"/>
+      <tableStyleElement type="headerRow" dxfId="528"/>
+      <tableStyleElement type="firstRowStripe" dxfId="527"/>
+      <tableStyleElement type="secondRowStripe" dxfId="526"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF45000000}">
       <tableStyleElement type="firstRowStripe" dxfId="525"/>
@@ -6970,10 +6970,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="516"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF4A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="512"/>
-      <tableStyleElement type="headerRow" dxfId="515"/>
-      <tableStyleElement type="firstRowStripe" dxfId="514"/>
-      <tableStyleElement type="secondRowStripe" dxfId="513"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="515"/>
+      <tableStyleElement type="headerRow" dxfId="514"/>
+      <tableStyleElement type="firstRowStripe" dxfId="513"/>
+      <tableStyleElement type="secondRowStripe" dxfId="512"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF4B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="511"/>
@@ -7560,10 +7560,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="220"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFFDD000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="216"/>
-      <tableStyleElement type="headerRow" dxfId="219"/>
-      <tableStyleElement type="firstRowStripe" dxfId="218"/>
-      <tableStyleElement type="secondRowStripe" dxfId="217"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="219"/>
+      <tableStyleElement type="headerRow" dxfId="218"/>
+      <tableStyleElement type="firstRowStripe" dxfId="217"/>
+      <tableStyleElement type="secondRowStripe" dxfId="216"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFFDE000000}">
       <tableStyleElement type="firstRowStripe" dxfId="215"/>
@@ -8443,18 +8443,18 @@
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
@@ -8496,7 +8496,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>17</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>19</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>21</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>22</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>23</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>24</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>30</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>31</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>32</v>
       </c>
@@ -9036,7 +9036,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>33</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>34</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>35</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>36</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>37</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>38</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>39</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>40</v>
       </c>
@@ -9252,7 +9252,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>41</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>42</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>43</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>44</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>46</v>
       </c>

--- a/backend/DATA_UPCOMING.xlsx
+++ b/backend/DATA_UPCOMING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D7FD85-8D9F-4E42-91E1-599FFA62CF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F62680-A899-4FD9-97CB-52509BCB0E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="2022 -2025 PRC DATA RECORD" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -8448,13 +8449,13 @@
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>

--- a/backend/DATA_UPCOMING.xlsx
+++ b/backend/DATA_UPCOMING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F62680-A899-4FD9-97CB-52509BCB0E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F26855-830F-4F59-B86E-4C66C2DC6172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8449,13 +8449,13 @@
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>

--- a/backend/DATA_UPCOMING.xlsx
+++ b/backend/DATA_UPCOMING.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F26855-830F-4F59-B86E-4C66C2DC6172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E21C62-BFA3-4B32-902D-FFBFE1065DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22845" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022 -2025 PRC DATA RECORD" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -8449,13 +8448,13 @@
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
